--- a/Functionalities.xlsx
+++ b/Functionalities.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeel Viradiya\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A7EE126-83CB-412C-BC62-79A97CEA5AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4DC4324D-7AD3-4456-BC34-783D0BCB5027}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>login</t>
   </si>
@@ -63,9 +57,6 @@
     <t>salary report</t>
   </si>
   <si>
-    <t>Assign task</t>
-  </si>
-  <si>
     <t>HR</t>
   </si>
   <si>
@@ -106,12 +97,27 @@
   </si>
   <si>
     <t>done</t>
+  </si>
+  <si>
+    <t>Create task</t>
+  </si>
+  <si>
+    <t>add leave</t>
+  </si>
+  <si>
+    <t>Approv leave</t>
+  </si>
+  <si>
+    <t>Leave History</t>
+  </si>
+  <si>
+    <t>previous leave status</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -212,7 +218,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -264,7 +270,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -458,15 +464,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17BE317A-5ECC-40E8-8D5B-D96F791A3F43}">
-  <dimension ref="A1:C30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.33203125" customWidth="1"/>
@@ -498,7 +504,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -506,7 +512,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -521,92 +527,127 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>15</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A26" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>21</v>
+      <c r="A28" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Functionalities.xlsx
+++ b/Functionalities.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>login</t>
   </si>
@@ -99,19 +99,22 @@
     <t>done</t>
   </si>
   <si>
-    <t>Create task</t>
-  </si>
-  <si>
     <t>add leave</t>
   </si>
   <si>
-    <t>Approv leave</t>
-  </si>
-  <si>
     <t>Leave History</t>
   </si>
   <si>
     <t>previous leave status</t>
+  </si>
+  <si>
+    <t>approv leave</t>
+  </si>
+  <si>
+    <t>leave history</t>
+  </si>
+  <si>
+    <t>Add task</t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -472,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.33203125" customWidth="1"/>
@@ -532,7 +535,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
@@ -540,114 +543,122 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>9</v>
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>23</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Functionalities.xlsx
+++ b/Functionalities.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>login</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>Add task</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pages </t>
   </si>
 </sst>
 </file>
@@ -467,7 +470,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -475,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.33203125" customWidth="1"/>
@@ -661,6 +664,11 @@
         <v>25</v>
       </c>
     </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Functionalities.xlsx
+++ b/Functionalities.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\WorkWave\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34D7020-4F8A-40EC-B0E3-735AB540AD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,21 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
   <si>
     <t>login</t>
   </si>
@@ -118,12 +115,21 @@
   </si>
   <si>
     <t xml:space="preserve">Pages </t>
+  </si>
+  <si>
+    <t>profile image</t>
+  </si>
+  <si>
+    <t>add_emp.php</t>
+  </si>
+  <si>
+    <t>add_leave.php</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -470,21 +476,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -495,178 +501,215 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>26</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>23</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Functionalities.xlsx
+++ b/Functionalities.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\WorkWave\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\_clg_project\WorkWave\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34D7020-4F8A-40EC-B0E3-735AB540AD16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7B366C-866F-48D2-A5F4-D6EC78917D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="48">
   <si>
     <t>login</t>
   </si>
@@ -124,6 +124,51 @@
   </si>
   <si>
     <t>add_leave.php</t>
+  </si>
+  <si>
+    <t>add_task.php</t>
+  </si>
+  <si>
+    <t>approve_leave.php</t>
+  </si>
+  <si>
+    <t>att.php</t>
+  </si>
+  <si>
+    <t>attendence.php</t>
+  </si>
+  <si>
+    <t>auth-login.php</t>
+  </si>
+  <si>
+    <t>index.php</t>
+  </si>
+  <si>
+    <t>leave_history.php</t>
+  </si>
+  <si>
+    <t>leave_status.php</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>emp</t>
+  </si>
+  <si>
+    <t>hr</t>
+  </si>
+  <si>
+    <t>dummmy</t>
+  </si>
+  <si>
+    <t>all(admin)</t>
+  </si>
+  <si>
+    <t>all(!all)</t>
+  </si>
+  <si>
+    <t>few changes needed</t>
   </si>
 </sst>
 </file>
@@ -230,7 +275,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -282,7 +327,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -484,13 +529,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.33203125" customWidth="1"/>
+    <col min="1" max="1" width="53.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -501,17 +546,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -522,7 +567,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -536,22 +581,28 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -562,7 +613,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -573,12 +624,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -589,17 +640,20 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -610,7 +664,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -621,67 +675,76 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -692,24 +755,100 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>32</v>
+      </c>
+      <c r="D43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Functionalities.xlsx
+++ b/Functionalities.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\_clg_project\WorkWave\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\WorkWave\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7B366C-866F-48D2-A5F4-D6EC78917D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470C3594-D944-4886-90A8-FD8F18F6ED7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="49">
   <si>
     <t>login</t>
   </si>
@@ -78,9 +78,6 @@
     <t>assign task</t>
   </si>
   <si>
-    <t>view progress</t>
-  </si>
-  <si>
     <t>view task</t>
   </si>
   <si>
@@ -162,13 +159,19 @@
     <t>dummmy</t>
   </si>
   <si>
-    <t>all(admin)</t>
-  </si>
-  <si>
-    <t>all(!all)</t>
-  </si>
-  <si>
     <t>few changes needed</t>
+  </si>
+  <si>
+    <t>pm</t>
+  </si>
+  <si>
+    <t>assign_task.php</t>
+  </si>
+  <si>
+    <t>task.php</t>
+  </si>
+  <si>
+    <t>view_task.php</t>
   </si>
 </sst>
 </file>
@@ -529,13 +532,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G54"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="53.28515625" customWidth="1"/>
+    <col min="1" max="1" width="53.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -546,309 +549,375 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>13</v>
       </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>26</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>18</v>
-      </c>
       <c r="B25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>31</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>32</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>33</v>
-      </c>
-      <c r="D44" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" t="s">
+        <v>40</v>
+      </c>
+      <c r="E47" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G47" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>34</v>
-      </c>
-      <c r="D45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>35</v>
-      </c>
-      <c r="D46" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>36</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
+        <v>40</v>
+      </c>
+      <c r="E48" t="s">
+        <v>42</v>
+      </c>
+      <c r="F48" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="G48" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>37</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
+        <v>40</v>
+      </c>
+      <c r="E49" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" t="s">
+        <v>45</v>
+      </c>
+      <c r="G49" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>38</v>
-      </c>
-      <c r="D49" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="D52" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" t="s">
         <v>41</v>
-      </c>
-      <c r="E50" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>40</v>
-      </c>
-      <c r="D51" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Functionalities.xlsx
+++ b/Functionalities.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\WorkWave\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470C3594-D944-4886-90A8-FD8F18F6ED7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="50">
   <si>
     <t>login</t>
   </si>
@@ -172,12 +166,15 @@
   </si>
   <si>
     <t>view_task.php</t>
+  </si>
+  <si>
+    <t>multiple record insert</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -278,7 +275,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -330,7 +327,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -524,15 +521,15 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.33203125" customWidth="1"/>
@@ -857,7 +854,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>37</v>
       </c>
@@ -874,7 +871,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>38</v>
       </c>
@@ -885,7 +882,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -893,15 +890,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>46</v>
       </c>
       <c r="D52" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>47</v>
       </c>
@@ -912,7 +912,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>48</v>
       </c>
